--- a/데이터/opened_course2023_2.xlsx
+++ b/데이터/opened_course2023_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\AI융개_팀플\데이터\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87DFCFE-D75A-4EF5-83A9-311A8EEB006C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4EDDB8D-8975-49ED-B834-F27E62DDA9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="심화전공2023_2" sheetId="4" r:id="rId1"/>
@@ -584,9 +584,6 @@
     <t>마이크로컨트롤러응용실습</t>
   </si>
   <si>
-    <t>지능형IoT</t>
-  </si>
-  <si>
     <t>디지털회로및실습</t>
   </si>
   <si>
@@ -705,9 +702,6 @@
   </si>
   <si>
     <t>IoT 서비스설계</t>
-  </si>
-  <si>
-    <t>서비스·디자인공학과</t>
   </si>
   <si>
     <t>미디어스토리텔링 프로덕션</t>
@@ -1009,6 +1003,14 @@
   </si>
   <si>
     <t>심화전공</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서비스디자인공학과</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지능형IoT</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1419,16 +1421,16 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -1436,16 +1438,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C3" t="s">
         <v>323</v>
       </c>
-      <c r="C3" t="s">
-        <v>325</v>
-      </c>
       <c r="D3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -1453,16 +1455,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C4" t="s">
         <v>323</v>
       </c>
-      <c r="C4" t="s">
-        <v>325</v>
-      </c>
       <c r="D4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1470,16 +1472,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -1487,16 +1489,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -1504,16 +1506,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B7" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C7" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -1521,16 +1523,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -1538,16 +1540,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B9" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C9" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -1555,16 +1557,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B10" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C10" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -1572,16 +1574,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B11" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C11" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D11" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -1589,16 +1591,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B12" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -1606,16 +1608,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B13" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C13" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D13" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -1623,16 +1625,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B14" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C14" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D14" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -1640,16 +1642,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B15" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C15" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D15" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -1657,16 +1659,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B16" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C16" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D16" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -1674,16 +1676,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C17" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D17" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -1691,16 +1693,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B18" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C18" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D18" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -1708,16 +1710,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B19" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C19" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D19" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -1725,16 +1727,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C20" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D20" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -1742,16 +1744,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B21" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C21" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D21" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -1759,16 +1761,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B22" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C22" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D22" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E22">
         <v>3</v>
@@ -1776,16 +1778,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C23" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D23" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E23">
         <v>3</v>
@@ -1793,16 +1795,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B24" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C24" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D24" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E24">
         <v>3</v>
@@ -1810,16 +1812,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C25" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D25" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E25">
         <v>3</v>
@@ -1827,16 +1829,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B26" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C26" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D26" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E26">
         <v>3</v>
@@ -1844,16 +1846,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B27" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C27" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D27" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E27">
         <v>3</v>
@@ -1861,16 +1863,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B28" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C28" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D28" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -1878,16 +1880,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B29" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C29" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D29" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -1895,16 +1897,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B30" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C30" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D30" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E30">
         <v>3</v>
@@ -1912,16 +1914,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B31" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C31" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D31" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E31">
         <v>3</v>
@@ -1929,16 +1931,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B32" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C32" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D32" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E32">
         <v>3</v>
@@ -1946,16 +1948,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C33" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D33" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E33">
         <v>3</v>
@@ -1963,16 +1965,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B34" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C34" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D34" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E34">
         <v>3</v>
@@ -1980,16 +1982,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B35" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C35" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D35" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E35">
         <v>3</v>
@@ -1997,16 +1999,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B36" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C36" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D36" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E36">
         <v>3</v>
@@ -2014,16 +2016,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B37" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C37" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D37" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E37">
         <v>3</v>
@@ -2031,16 +2033,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B38" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C38" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D38" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E38">
         <v>3</v>
@@ -2048,16 +2050,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B39" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C39" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D39" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E39">
         <v>3</v>
@@ -2065,16 +2067,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B40" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C40" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D40" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E40">
         <v>3</v>
@@ -2082,16 +2084,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B41" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C41" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D41" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E41">
         <v>3</v>
@@ -2099,16 +2101,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B42" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C42" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D42" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E42">
         <v>3</v>
@@ -2116,16 +2118,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B43" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C43" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D43" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E43">
         <v>3</v>
@@ -2133,16 +2135,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B44" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C44" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D44" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E44">
         <v>3</v>
@@ -2150,16 +2152,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B45" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C45" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D45" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E45">
         <v>3</v>
@@ -2167,16 +2169,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B46" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C46" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E46">
         <v>3</v>
@@ -2184,16 +2186,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B47" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C47" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D47" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E47">
         <v>3</v>
@@ -2201,16 +2203,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B48" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C48" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D48" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E48">
         <v>3</v>
@@ -2218,16 +2220,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B49" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C49" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D49" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E49">
         <v>3</v>
@@ -2235,16 +2237,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B50" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C50" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D50" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E50">
         <v>3</v>
@@ -2252,16 +2254,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B51" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C51" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D51" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E51">
         <v>3</v>
@@ -2269,16 +2271,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B52" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C52" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D52" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -2286,16 +2288,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B53" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C53" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D53" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E53">
         <v>3</v>
@@ -2303,16 +2305,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B54" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C54" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D54" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -2320,16 +2322,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B55" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C55" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D55" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E55">
         <v>3</v>
@@ -2337,16 +2339,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B56" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C56" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D56" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E56">
         <v>3</v>
@@ -2354,16 +2356,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B57" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C57" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D57" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E57">
         <v>3</v>
@@ -2371,16 +2373,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B58" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C58" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D58" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E58">
         <v>3</v>
@@ -2388,16 +2390,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B59" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C59" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D59" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -2408,13 +2410,13 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C60" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D60" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E60">
         <v>3</v>
@@ -2425,13 +2427,13 @@
         <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C61" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D61" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E61">
         <v>3</v>
@@ -2442,13 +2444,13 @@
         <v>66</v>
       </c>
       <c r="B62" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C62" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D62" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -2459,13 +2461,13 @@
         <v>66</v>
       </c>
       <c r="B63" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C63" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D63" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E63">
         <v>3</v>
@@ -2476,13 +2478,13 @@
         <v>66</v>
       </c>
       <c r="B64" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C64" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D64" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E64">
         <v>2</v>
@@ -2493,13 +2495,13 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C65" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D65" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E65">
         <v>2</v>
@@ -2510,13 +2512,13 @@
         <v>66</v>
       </c>
       <c r="B66" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C66" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D66" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E66">
         <v>2</v>
@@ -2527,13 +2529,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C67" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D67" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E67">
         <v>3</v>
@@ -2544,13 +2546,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C68" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D68" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E68">
         <v>2</v>
@@ -2561,13 +2563,13 @@
         <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C69" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D69" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E69">
         <v>3</v>
@@ -2578,13 +2580,13 @@
         <v>66</v>
       </c>
       <c r="B70" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C70" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D70" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E70">
         <v>3</v>
@@ -2592,16 +2594,16 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B71" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C71" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D71" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E71">
         <v>3</v>
@@ -2609,16 +2611,16 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B72" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C72" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D72" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E72">
         <v>3</v>
@@ -2626,16 +2628,16 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B73" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C73" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D73" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E73">
         <v>3</v>
@@ -2643,16 +2645,16 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B74" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C74" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D74" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E74">
         <v>3</v>
@@ -2660,16 +2662,16 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B75" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C75" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D75" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E75">
         <v>3</v>
@@ -2677,16 +2679,16 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B76" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C76" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D76" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E76">
         <v>3</v>
@@ -2694,16 +2696,16 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>184</v>
+        <v>325</v>
       </c>
       <c r="B77" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C77" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D77" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E77">
         <v>3</v>
@@ -2711,16 +2713,16 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>184</v>
+        <v>325</v>
       </c>
       <c r="B78" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C78" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D78" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E78">
         <v>3</v>
@@ -2761,16 +2763,16 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C2" t="s">
         <v>182</v>
       </c>
       <c r="D2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -2778,16 +2780,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B3" t="s">
         <v>260</v>
       </c>
-      <c r="B3" t="s">
-        <v>262</v>
-      </c>
       <c r="C3" t="s">
         <v>182</v>
       </c>
       <c r="D3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -2795,16 +2797,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B4" t="s">
         <v>260</v>
       </c>
-      <c r="B4" t="s">
-        <v>262</v>
-      </c>
       <c r="C4" t="s">
         <v>182</v>
       </c>
       <c r="D4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -2812,16 +2814,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B5" t="s">
         <v>260</v>
       </c>
-      <c r="B5" t="s">
-        <v>262</v>
-      </c>
       <c r="C5" t="s">
         <v>182</v>
       </c>
       <c r="D5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -2829,16 +2831,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B6" t="s">
         <v>260</v>
       </c>
-      <c r="B6" t="s">
-        <v>262</v>
-      </c>
       <c r="C6" t="s">
         <v>182</v>
       </c>
       <c r="D6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -2846,16 +2848,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C7" t="s">
         <v>182</v>
       </c>
       <c r="D7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -2863,16 +2865,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C8" t="s">
         <v>182</v>
       </c>
       <c r="D8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -2880,10 +2882,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C9" t="s">
         <v>182</v>
@@ -2897,10 +2899,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C10" t="s">
         <v>182</v>
@@ -2914,10 +2916,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
+        <v>252</v>
+      </c>
+      <c r="B11" t="s">
         <v>254</v>
-      </c>
-      <c r="B11" t="s">
-        <v>256</v>
       </c>
       <c r="C11" t="s">
         <v>182</v>
@@ -2931,10 +2933,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B12" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C12" t="s">
         <v>182</v>
@@ -2948,10 +2950,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B13" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C13" t="s">
         <v>182</v>
@@ -2965,16 +2967,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B14" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C14" t="s">
         <v>182</v>
       </c>
       <c r="D14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -2982,16 +2984,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B15" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C15" t="s">
         <v>182</v>
       </c>
       <c r="D15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -2999,10 +3001,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B16" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C16" t="s">
         <v>182</v>
@@ -3016,10 +3018,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B17" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C17" t="s">
         <v>182</v>
@@ -3033,10 +3035,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
+        <v>245</v>
+      </c>
+      <c r="B18" t="s">
         <v>247</v>
-      </c>
-      <c r="B18" t="s">
-        <v>249</v>
       </c>
       <c r="C18" t="s">
         <v>182</v>
@@ -3050,10 +3052,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
+        <v>245</v>
+      </c>
+      <c r="B19" t="s">
         <v>247</v>
-      </c>
-      <c r="B19" t="s">
-        <v>249</v>
       </c>
       <c r="C19" t="s">
         <v>182</v>
@@ -3067,10 +3069,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B20" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C20" t="s">
         <v>182</v>
@@ -3084,10 +3086,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C21" t="s">
         <v>182</v>
@@ -3101,10 +3103,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C22" t="s">
         <v>182</v>
@@ -3118,10 +3120,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C23" t="s">
         <v>182</v>
@@ -3135,16 +3137,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C24" t="s">
         <v>182</v>
       </c>
       <c r="D24" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E24">
         <v>3</v>
@@ -3152,10 +3154,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B25" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C25" t="s">
         <v>182</v>
@@ -3169,10 +3171,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C26" t="s">
         <v>182</v>
@@ -3189,13 +3191,13 @@
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C27" t="s">
         <v>182</v>
       </c>
       <c r="D27" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E27">
         <v>3</v>
@@ -3206,13 +3208,13 @@
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C28" t="s">
         <v>182</v>
       </c>
       <c r="D28" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -3223,13 +3225,13 @@
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C29" t="s">
         <v>182</v>
       </c>
       <c r="D29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -3240,13 +3242,13 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C30" t="s">
         <v>182</v>
       </c>
       <c r="D30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E30">
         <v>3</v>
@@ -3257,13 +3259,13 @@
         <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C31" t="s">
         <v>182</v>
       </c>
       <c r="D31" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E31">
         <v>3</v>
@@ -3274,13 +3276,13 @@
         <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C32" t="s">
         <v>182</v>
       </c>
       <c r="D32" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E32">
         <v>3</v>
@@ -3291,13 +3293,13 @@
         <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C33" t="s">
         <v>182</v>
       </c>
       <c r="D33" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E33">
         <v>3</v>
@@ -3308,13 +3310,13 @@
         <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C34" t="s">
         <v>182</v>
       </c>
       <c r="D34" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E34">
         <v>3</v>
@@ -3325,13 +3327,13 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C35" t="s">
         <v>182</v>
       </c>
       <c r="D35" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E35">
         <v>3</v>
@@ -3342,13 +3344,13 @@
         <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C36" t="s">
         <v>182</v>
       </c>
       <c r="D36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E36">
         <v>3</v>
@@ -3359,13 +3361,13 @@
         <v>2</v>
       </c>
       <c r="B37" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C37" t="s">
         <v>182</v>
       </c>
       <c r="D37" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E37">
         <v>3</v>
@@ -3376,13 +3378,13 @@
         <v>2</v>
       </c>
       <c r="B38" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C38" t="s">
         <v>182</v>
       </c>
       <c r="D38" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E38">
         <v>3</v>
@@ -3393,13 +3395,13 @@
         <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C39" t="s">
         <v>182</v>
       </c>
       <c r="D39" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E39">
         <v>3</v>
@@ -3410,13 +3412,13 @@
         <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C40" t="s">
         <v>182</v>
       </c>
       <c r="D40" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E40">
         <v>3</v>
@@ -3427,13 +3429,13 @@
         <v>2</v>
       </c>
       <c r="B41" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C41" t="s">
         <v>182</v>
       </c>
       <c r="D41" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E41">
         <v>3</v>
@@ -3444,13 +3446,13 @@
         <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C42" t="s">
         <v>182</v>
       </c>
       <c r="D42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E42">
         <v>3</v>
@@ -3461,13 +3463,13 @@
         <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C43" t="s">
         <v>182</v>
       </c>
       <c r="D43" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E43">
         <v>3</v>
@@ -3478,13 +3480,13 @@
         <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C44" t="s">
         <v>182</v>
       </c>
       <c r="D44" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E44">
         <v>3</v>
@@ -3495,13 +3497,13 @@
         <v>2</v>
       </c>
       <c r="B45" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C45" t="s">
         <v>182</v>
       </c>
       <c r="D45" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E45">
         <v>3</v>
@@ -3512,13 +3514,13 @@
         <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C46" t="s">
         <v>182</v>
       </c>
       <c r="D46" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E46">
         <v>3</v>
@@ -3529,13 +3531,13 @@
         <v>2</v>
       </c>
       <c r="B47" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C47" t="s">
         <v>182</v>
       </c>
       <c r="D47" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E47">
         <v>3</v>
@@ -3546,13 +3548,13 @@
         <v>2</v>
       </c>
       <c r="B48" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C48" t="s">
         <v>182</v>
       </c>
       <c r="D48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E48">
         <v>3</v>
@@ -3563,13 +3565,13 @@
         <v>2</v>
       </c>
       <c r="B49" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C49" t="s">
         <v>182</v>
       </c>
       <c r="D49" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E49">
         <v>3</v>
@@ -3580,13 +3582,13 @@
         <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C50" t="s">
         <v>182</v>
       </c>
       <c r="D50" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E50">
         <v>3</v>
@@ -3597,7 +3599,7 @@
         <v>2</v>
       </c>
       <c r="B51" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C51" t="s">
         <v>182</v>
@@ -3614,7 +3616,7 @@
         <v>2</v>
       </c>
       <c r="B52" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C52" t="s">
         <v>182</v>
@@ -3631,7 +3633,7 @@
         <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C53" t="s">
         <v>182</v>
@@ -3648,7 +3650,7 @@
         <v>2</v>
       </c>
       <c r="B54" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C54" t="s">
         <v>182</v>
@@ -3665,7 +3667,7 @@
         <v>2</v>
       </c>
       <c r="B55" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C55" t="s">
         <v>182</v>
@@ -3682,7 +3684,7 @@
         <v>2</v>
       </c>
       <c r="B56" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C56" t="s">
         <v>182</v>
@@ -3699,7 +3701,7 @@
         <v>2</v>
       </c>
       <c r="B57" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C57" t="s">
         <v>182</v>
@@ -3716,7 +3718,7 @@
         <v>2</v>
       </c>
       <c r="B58" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C58" t="s">
         <v>182</v>
@@ -3733,7 +3735,7 @@
         <v>2</v>
       </c>
       <c r="B59" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C59" t="s">
         <v>182</v>
@@ -3747,16 +3749,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B60" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C60" t="s">
         <v>182</v>
       </c>
       <c r="D60" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E60">
         <v>3</v>
@@ -3764,16 +3766,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B61" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C61" t="s">
         <v>182</v>
       </c>
       <c r="D61" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E61">
         <v>3</v>
@@ -3781,10 +3783,10 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B62" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C62" t="s">
         <v>182</v>
@@ -3798,10 +3800,10 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B63" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C63" t="s">
         <v>182</v>
@@ -3815,10 +3817,10 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B64" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C64" t="s">
         <v>182</v>
@@ -3832,10 +3834,10 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
+        <v>324</v>
+      </c>
+      <c r="B65" t="s">
         <v>225</v>
-      </c>
-      <c r="B65" t="s">
-        <v>227</v>
       </c>
       <c r="C65" t="s">
         <v>182</v>
@@ -3849,10 +3851,10 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
+        <v>324</v>
+      </c>
+      <c r="B66" t="s">
         <v>225</v>
-      </c>
-      <c r="B66" t="s">
-        <v>227</v>
       </c>
       <c r="C66" t="s">
         <v>182</v>
@@ -3866,10 +3868,10 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B67" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C67" t="s">
         <v>182</v>
@@ -3883,10 +3885,10 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B68" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C68" t="s">
         <v>182</v>
@@ -3900,10 +3902,10 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B69" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C69" t="s">
         <v>182</v>
@@ -3917,10 +3919,10 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B70" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C70" t="s">
         <v>182</v>
@@ -3934,10 +3936,10 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
+        <v>221</v>
+      </c>
+      <c r="B71" t="s">
         <v>222</v>
-      </c>
-      <c r="B71" t="s">
-        <v>223</v>
       </c>
       <c r="C71" t="s">
         <v>182</v>
@@ -3951,10 +3953,10 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B72" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C72" t="s">
         <v>182</v>
@@ -3968,10 +3970,10 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
+        <v>218</v>
+      </c>
+      <c r="B73" t="s">
         <v>219</v>
-      </c>
-      <c r="B73" t="s">
-        <v>220</v>
       </c>
       <c r="C73" t="s">
         <v>182</v>
@@ -3985,10 +3987,10 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B74" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C74" t="s">
         <v>182</v>
@@ -4002,10 +4004,10 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B75" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C75" t="s">
         <v>182</v>
@@ -4019,16 +4021,16 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B76" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C76" t="s">
         <v>182</v>
       </c>
       <c r="D76" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E76">
         <v>3</v>
@@ -4036,16 +4038,16 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B77" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C77" t="s">
         <v>182</v>
       </c>
       <c r="D77" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E77">
         <v>2</v>
@@ -4053,16 +4055,16 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B78" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C78" t="s">
         <v>182</v>
       </c>
       <c r="D78" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E78">
         <v>2</v>
@@ -4070,16 +4072,16 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B79" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C79" t="s">
         <v>182</v>
       </c>
       <c r="D79" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E79">
         <v>2</v>
@@ -4087,10 +4089,10 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B80" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C80" t="s">
         <v>182</v>
@@ -4104,10 +4106,10 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B81" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C81" t="s">
         <v>182</v>
@@ -4121,10 +4123,10 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B82" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C82" t="s">
         <v>182</v>
@@ -4138,10 +4140,10 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
+        <v>210</v>
+      </c>
+      <c r="B83" t="s">
         <v>211</v>
-      </c>
-      <c r="B83" t="s">
-        <v>212</v>
       </c>
       <c r="C83" t="s">
         <v>182</v>
@@ -4155,10 +4157,10 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B84" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C84" t="s">
         <v>182</v>
@@ -4172,16 +4174,16 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B85" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C85" t="s">
         <v>182</v>
       </c>
       <c r="D85" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E85">
         <v>3</v>
@@ -4189,16 +4191,16 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B86" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C86" t="s">
         <v>182</v>
       </c>
       <c r="D86" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E86">
         <v>3</v>
@@ -4206,16 +4208,16 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B87" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C87" t="s">
         <v>182</v>
       </c>
       <c r="D87" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E87">
         <v>3</v>
@@ -4223,10 +4225,10 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B88" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C88" t="s">
         <v>182</v>
@@ -4240,10 +4242,10 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B89" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C89" t="s">
         <v>182</v>
@@ -4257,10 +4259,10 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B90" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C90" t="s">
         <v>182</v>
@@ -4274,10 +4276,10 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
+        <v>201</v>
+      </c>
+      <c r="B91" t="s">
         <v>202</v>
-      </c>
-      <c r="B91" t="s">
-        <v>203</v>
       </c>
       <c r="C91" t="s">
         <v>182</v>
@@ -4291,10 +4293,10 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
+        <v>201</v>
+      </c>
+      <c r="B92" t="s">
         <v>202</v>
-      </c>
-      <c r="B92" t="s">
-        <v>203</v>
       </c>
       <c r="C92" t="s">
         <v>182</v>
@@ -4308,10 +4310,10 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B93" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C93" t="s">
         <v>182</v>
@@ -4328,13 +4330,13 @@
         <v>66</v>
       </c>
       <c r="B94" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C94" t="s">
         <v>182</v>
       </c>
       <c r="D94" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E94">
         <v>3</v>
@@ -4345,13 +4347,13 @@
         <v>66</v>
       </c>
       <c r="B95" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C95" t="s">
         <v>182</v>
       </c>
       <c r="D95" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E95">
         <v>2</v>
@@ -4362,13 +4364,13 @@
         <v>66</v>
       </c>
       <c r="B96" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C96" t="s">
         <v>182</v>
       </c>
       <c r="D96" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E96">
         <v>2</v>
@@ -4379,13 +4381,13 @@
         <v>66</v>
       </c>
       <c r="B97" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C97" t="s">
         <v>182</v>
       </c>
       <c r="D97" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E97">
         <v>2</v>
@@ -4396,13 +4398,13 @@
         <v>66</v>
       </c>
       <c r="B98" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C98" t="s">
         <v>182</v>
       </c>
       <c r="D98" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E98">
         <v>2</v>
@@ -4413,13 +4415,13 @@
         <v>66</v>
       </c>
       <c r="B99" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C99" t="s">
         <v>182</v>
       </c>
       <c r="D99" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E99">
         <v>2</v>
@@ -4430,13 +4432,13 @@
         <v>66</v>
       </c>
       <c r="B100" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C100" t="s">
         <v>182</v>
       </c>
       <c r="D100" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E100">
         <v>2</v>
@@ -4447,13 +4449,13 @@
         <v>66</v>
       </c>
       <c r="B101" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C101" t="s">
         <v>182</v>
       </c>
       <c r="D101" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E101">
         <v>2</v>
@@ -4464,7 +4466,7 @@
         <v>66</v>
       </c>
       <c r="B102" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C102" t="s">
         <v>182</v>
@@ -4481,7 +4483,7 @@
         <v>66</v>
       </c>
       <c r="B103" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C103" t="s">
         <v>182</v>
@@ -4498,7 +4500,7 @@
         <v>66</v>
       </c>
       <c r="B104" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C104" t="s">
         <v>182</v>
@@ -4515,7 +4517,7 @@
         <v>66</v>
       </c>
       <c r="B105" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C105" t="s">
         <v>182</v>
@@ -4532,7 +4534,7 @@
         <v>66</v>
       </c>
       <c r="B106" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C106" t="s">
         <v>182</v>
@@ -4549,7 +4551,7 @@
         <v>66</v>
       </c>
       <c r="B107" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C107" t="s">
         <v>182</v>
@@ -4563,16 +4565,16 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B108" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C108" t="s">
         <v>182</v>
       </c>
       <c r="D108" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E108">
         <v>3</v>
@@ -4580,10 +4582,10 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B109" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C109" t="s">
         <v>182</v>
@@ -4597,10 +4599,10 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B110" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C110" t="s">
         <v>182</v>
@@ -4614,10 +4616,10 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
+        <v>188</v>
+      </c>
+      <c r="B111" t="s">
         <v>189</v>
-      </c>
-      <c r="B111" t="s">
-        <v>190</v>
       </c>
       <c r="C111" t="s">
         <v>182</v>
@@ -4631,10 +4633,10 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
+        <v>188</v>
+      </c>
+      <c r="B112" t="s">
         <v>189</v>
-      </c>
-      <c r="B112" t="s">
-        <v>190</v>
       </c>
       <c r="C112" t="s">
         <v>182</v>
@@ -4648,10 +4650,10 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B113" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C113" t="s">
         <v>182</v>
@@ -4665,10 +4667,10 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B114" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C114" t="s">
         <v>182</v>
@@ -4682,10 +4684,10 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B115" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C115" t="s">
         <v>182</v>
@@ -4699,10 +4701,10 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B116" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C116" t="s">
         <v>182</v>
@@ -4716,10 +4718,10 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B117" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C117" t="s">
         <v>182</v>
@@ -4733,10 +4735,10 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
+        <v>325</v>
+      </c>
+      <c r="B118" t="s">
         <v>184</v>
-      </c>
-      <c r="B118" t="s">
-        <v>185</v>
       </c>
       <c r="C118" t="s">
         <v>182</v>
@@ -4750,7 +4752,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
-        <v>184</v>
+        <v>325</v>
       </c>
       <c r="B119" t="s">
         <v>183</v>
@@ -6793,7 +6795,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D2" t="s">
         <v>57</v>
@@ -6810,7 +6812,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D3" t="s">
         <v>57</v>
@@ -6827,7 +6829,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D4" t="s">
         <v>57</v>
@@ -6844,7 +6846,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D5" t="s">
         <v>57</v>
@@ -6861,7 +6863,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D6" t="s">
         <v>57</v>
@@ -6878,7 +6880,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D7" t="s">
         <v>57</v>
@@ -6895,7 +6897,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D8" t="s">
         <v>57</v>
@@ -6912,7 +6914,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D9" t="s">
         <v>57</v>
@@ -6929,7 +6931,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D10" t="s">
         <v>57</v>
@@ -6946,7 +6948,7 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D11" t="s">
         <v>57</v>
@@ -6963,7 +6965,7 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D12" t="s">
         <v>57</v>
@@ -6980,7 +6982,7 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D13" t="s">
         <v>57</v>
@@ -6997,7 +6999,7 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D14" t="s">
         <v>57</v>
@@ -7014,7 +7016,7 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D15" t="s">
         <v>57</v>
@@ -7031,7 +7033,7 @@
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D16" t="s">
         <v>57</v>
@@ -7048,7 +7050,7 @@
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D17" t="s">
         <v>57</v>
@@ -7065,7 +7067,7 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D18" t="s">
         <v>57</v>
@@ -7082,7 +7084,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D19" t="s">
         <v>57</v>
@@ -7099,7 +7101,7 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D20" t="s">
         <v>57</v>
@@ -7116,7 +7118,7 @@
         <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D21" t="s">
         <v>57</v>
@@ -7133,7 +7135,7 @@
         <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D22" t="s">
         <v>57</v>
@@ -7150,7 +7152,7 @@
         <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D23" t="s">
         <v>57</v>
@@ -7167,7 +7169,7 @@
         <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D24" t="s">
         <v>57</v>
@@ -7184,7 +7186,7 @@
         <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D25" t="s">
         <v>57</v>
@@ -7201,7 +7203,7 @@
         <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D26" t="s">
         <v>57</v>
@@ -7218,7 +7220,7 @@
         <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D27" t="s">
         <v>57</v>
@@ -7235,7 +7237,7 @@
         <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D28" t="s">
         <v>57</v>
@@ -7252,7 +7254,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D29" t="s">
         <v>57</v>
@@ -7269,7 +7271,7 @@
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D30" t="s">
         <v>57</v>
@@ -7286,7 +7288,7 @@
         <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D31" t="s">
         <v>57</v>
@@ -7303,7 +7305,7 @@
         <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D32" t="s">
         <v>57</v>
@@ -7320,7 +7322,7 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D33" t="s">
         <v>57</v>
@@ -7337,7 +7339,7 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D34" t="s">
         <v>57</v>
@@ -7354,7 +7356,7 @@
         <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D35" t="s">
         <v>57</v>
@@ -7371,7 +7373,7 @@
         <v>19</v>
       </c>
       <c r="C36" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D36" t="s">
         <v>58</v>
@@ -7388,7 +7390,7 @@
         <v>19</v>
       </c>
       <c r="C37" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D37" t="s">
         <v>58</v>
@@ -7405,7 +7407,7 @@
         <v>19</v>
       </c>
       <c r="C38" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D38" t="s">
         <v>58</v>
@@ -7422,7 +7424,7 @@
         <v>19</v>
       </c>
       <c r="C39" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D39" t="s">
         <v>58</v>
@@ -7439,7 +7441,7 @@
         <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D40" t="s">
         <v>58</v>
@@ -7456,7 +7458,7 @@
         <v>20</v>
       </c>
       <c r="C41" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D41" t="s">
         <v>58</v>
@@ -7473,7 +7475,7 @@
         <v>20</v>
       </c>
       <c r="C42" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D42" t="s">
         <v>58</v>
@@ -7490,7 +7492,7 @@
         <v>20</v>
       </c>
       <c r="C43" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D43" t="s">
         <v>58</v>
@@ -7507,7 +7509,7 @@
         <v>21</v>
       </c>
       <c r="C44" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D44" t="s">
         <v>58</v>
@@ -7524,7 +7526,7 @@
         <v>21</v>
       </c>
       <c r="C45" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D45" t="s">
         <v>58</v>
@@ -7541,7 +7543,7 @@
         <v>22</v>
       </c>
       <c r="C46" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D46" t="s">
         <v>58</v>
@@ -7558,7 +7560,7 @@
         <v>22</v>
       </c>
       <c r="C47" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D47" t="s">
         <v>58</v>
@@ -7575,7 +7577,7 @@
         <v>23</v>
       </c>
       <c r="C48" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D48" t="s">
         <v>58</v>
@@ -7592,7 +7594,7 @@
         <v>24</v>
       </c>
       <c r="C49" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D49" t="s">
         <v>58</v>
@@ -7609,7 +7611,7 @@
         <v>25</v>
       </c>
       <c r="C50" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D50" t="s">
         <v>59</v>
@@ -7626,7 +7628,7 @@
         <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D51" t="s">
         <v>59</v>
@@ -7643,7 +7645,7 @@
         <v>27</v>
       </c>
       <c r="C52" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D52" t="s">
         <v>59</v>
@@ -7660,7 +7662,7 @@
         <v>28</v>
       </c>
       <c r="C53" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D53" t="s">
         <v>59</v>
@@ -7677,7 +7679,7 @@
         <v>29</v>
       </c>
       <c r="C54" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D54" t="s">
         <v>57</v>
@@ -7694,7 +7696,7 @@
         <v>30</v>
       </c>
       <c r="C55" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D55" t="s">
         <v>57</v>
@@ -7711,7 +7713,7 @@
         <v>31</v>
       </c>
       <c r="C56" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D56" t="s">
         <v>59</v>
@@ -7728,7 +7730,7 @@
         <v>32</v>
       </c>
       <c r="C57" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D57" t="s">
         <v>59</v>
@@ -7745,7 +7747,7 @@
         <v>33</v>
       </c>
       <c r="C58" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D58" t="s">
         <v>59</v>
@@ -7762,7 +7764,7 @@
         <v>34</v>
       </c>
       <c r="C59" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D59" t="s">
         <v>59</v>
@@ -7779,7 +7781,7 @@
         <v>35</v>
       </c>
       <c r="C60" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D60" t="s">
         <v>60</v>
@@ -7796,7 +7798,7 @@
         <v>36</v>
       </c>
       <c r="C61" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D61" t="s">
         <v>59</v>
@@ -7813,7 +7815,7 @@
         <v>37</v>
       </c>
       <c r="C62" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D62" t="s">
         <v>59</v>
@@ -7830,7 +7832,7 @@
         <v>38</v>
       </c>
       <c r="C63" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D63" t="s">
         <v>59</v>
@@ -7847,7 +7849,7 @@
         <v>39</v>
       </c>
       <c r="C64" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D64" t="s">
         <v>59</v>
@@ -7864,7 +7866,7 @@
         <v>40</v>
       </c>
       <c r="C65" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D65" t="s">
         <v>59</v>
@@ -7881,7 +7883,7 @@
         <v>41</v>
       </c>
       <c r="C66" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D66" t="s">
         <v>61</v>
@@ -7898,7 +7900,7 @@
         <v>42</v>
       </c>
       <c r="C67" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D67" t="s">
         <v>61</v>
@@ -7915,7 +7917,7 @@
         <v>43</v>
       </c>
       <c r="C68" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D68" t="s">
         <v>61</v>
@@ -7932,7 +7934,7 @@
         <v>44</v>
       </c>
       <c r="C69" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D69" t="s">
         <v>57</v>
@@ -7949,7 +7951,7 @@
         <v>45</v>
       </c>
       <c r="C70" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D70" t="s">
         <v>58</v>
@@ -7966,7 +7968,7 @@
         <v>46</v>
       </c>
       <c r="C71" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D71" t="s">
         <v>58</v>
@@ -7983,7 +7985,7 @@
         <v>47</v>
       </c>
       <c r="C72" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D72" t="s">
         <v>58</v>
@@ -8000,7 +8002,7 @@
         <v>48</v>
       </c>
       <c r="C73" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D73" t="s">
         <v>58</v>
@@ -8017,7 +8019,7 @@
         <v>49</v>
       </c>
       <c r="C74" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D74" t="s">
         <v>58</v>
@@ -8034,7 +8036,7 @@
         <v>50</v>
       </c>
       <c r="C75" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D75" t="s">
         <v>57</v>
@@ -8051,7 +8053,7 @@
         <v>51</v>
       </c>
       <c r="C76" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D76" t="s">
         <v>60</v>
@@ -8068,7 +8070,7 @@
         <v>51</v>
       </c>
       <c r="C77" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D77" t="s">
         <v>60</v>
@@ -8085,7 +8087,7 @@
         <v>51</v>
       </c>
       <c r="C78" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D78" t="s">
         <v>60</v>
@@ -8102,7 +8104,7 @@
         <v>51</v>
       </c>
       <c r="C79" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D79" t="s">
         <v>60</v>
@@ -8119,7 +8121,7 @@
         <v>51</v>
       </c>
       <c r="C80" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D80" t="s">
         <v>60</v>
@@ -8136,7 +8138,7 @@
         <v>52</v>
       </c>
       <c r="C81" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D81" t="s">
         <v>60</v>
@@ -8153,7 +8155,7 @@
         <v>52</v>
       </c>
       <c r="C82" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D82" t="s">
         <v>60</v>
@@ -8170,7 +8172,7 @@
         <v>52</v>
       </c>
       <c r="C83" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D83" t="s">
         <v>60</v>
@@ -8187,7 +8189,7 @@
         <v>52</v>
       </c>
       <c r="C84" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D84" t="s">
         <v>60</v>
@@ -8204,7 +8206,7 @@
         <v>52</v>
       </c>
       <c r="C85" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D85" t="s">
         <v>60</v>
@@ -8221,7 +8223,7 @@
         <v>53</v>
       </c>
       <c r="C86" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D86" t="s">
         <v>59</v>
@@ -8238,7 +8240,7 @@
         <v>53</v>
       </c>
       <c r="C87" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D87" t="s">
         <v>59</v>
@@ -8255,7 +8257,7 @@
         <v>53</v>
       </c>
       <c r="C88" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D88" t="s">
         <v>59</v>
@@ -8272,7 +8274,7 @@
         <v>54</v>
       </c>
       <c r="C89" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D89" t="s">
         <v>59</v>
